--- a/outputs/59884.xlsx
+++ b/outputs/59884.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
   <si>
     <t xml:space="preserve">1st</t>
   </si>
@@ -148,7 +148,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -341,13 +341,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -364,7 +364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -381,36 +381,17 @@
       <c r="H2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I2" s="1" t="n">
-        <f aca="false">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE($A$2:$A$13)),1),"")</f>
-        <v>1</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <f aca="false">IF($I2="","",COUNTIF($A$2:$A$13,$I2))</f>
-        <v>3</v>
-      </c>
-      <c r="K2" s="1" t="str">
-        <f aca="false" t="array" ref="K2:K2">IF($I2="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I2,ROW($B$2:$B$13)-ROW($B$2)+1),1)),""))</f>
-        <v>a</v>
-      </c>
-      <c r="L2" s="1" t="str">
-        <f aca="false" t="array" ref="L2:L2">IF($I2="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I2,ROW($B$2:$B$13)-ROW($B$2)+1),2)),""))</f>
-        <v>b</v>
-      </c>
-      <c r="M2" s="1" t="str">
-        <f aca="false" t="array" ref="M2:M2">IF($I2="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I2,ROW($B$2:$B$13)-ROW($B$2)+1),3)),""))</f>
-        <v>c</v>
-      </c>
-      <c r="N2" s="1" t="str">
-        <f aca="false" t="array" ref="N2:N2">IF($I2="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I2,ROW($B$2:$B$13)-ROW($B$2)+1),4)),""))</f>
-        <v/>
-      </c>
-      <c r="O2" s="1" t="str">
-        <f aca="false" t="array" ref="O2:O2">IF($I2="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I2,ROW($B$2:$B$13)-ROW($B$2)+1),5)),""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -426,36 +407,20 @@
       <c r="H3" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I3" s="1" t="n">
-        <f aca="false">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE($A$2:$A$13)),2),"")</f>
-        <v>2</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <f aca="false">IF($I3="","",COUNTIF($A$2:$A$13,$I3))</f>
-        <v>4</v>
-      </c>
-      <c r="K3" s="1" t="str">
-        <f aca="false" t="array" ref="K3:K3">IF($I3="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I3,ROW($B$2:$B$13)-ROW($B$2)+1),1)),""))</f>
-        <v>x</v>
-      </c>
-      <c r="L3" s="1" t="str">
-        <f aca="false" t="array" ref="L3:L3">IF($I3="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I3,ROW($B$2:$B$13)-ROW($B$2)+1),2)),""))</f>
-        <v>w</v>
-      </c>
-      <c r="M3" s="1" t="str">
-        <f aca="false" t="array" ref="M3:M3">IF($I3="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I3,ROW($B$2:$B$13)-ROW($B$2)+1),3)),""))</f>
-        <v>y</v>
-      </c>
-      <c r="N3" s="1" t="str">
-        <f aca="false" t="array" ref="N3:N3">IF($I3="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I3,ROW($B$2:$B$13)-ROW($B$2)+1),4)),""))</f>
-        <v>z</v>
-      </c>
-      <c r="O3" s="1" t="str">
-        <f aca="false" t="array" ref="O3:O3">IF($I3="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I3,ROW($B$2:$B$13)-ROW($B$2)+1),5)),""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
@@ -471,36 +436,23 @@
       <c r="H4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I4" s="1" t="n">
-        <f aca="false">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE($A$2:$A$13)),3),"")</f>
-        <v>3</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <f aca="false">IF($I4="","",COUNTIF($A$2:$A$13,$I4))</f>
-        <v>5</v>
-      </c>
-      <c r="K4" s="1" t="str">
-        <f aca="false" t="array" ref="K4:K4">IF($I4="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I4,ROW($B$2:$B$13)-ROW($B$2)+1),1)),""))</f>
-        <v>aa</v>
-      </c>
-      <c r="L4" s="1" t="str">
-        <f aca="false" t="array" ref="L4:L4">IF($I4="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I4,ROW($B$2:$B$13)-ROW($B$2)+1),2)),""))</f>
-        <v>ab</v>
-      </c>
-      <c r="M4" s="1" t="str">
-        <f aca="false" t="array" ref="M4:M4">IF($I4="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I4,ROW($B$2:$B$13)-ROW($B$2)+1),3)),""))</f>
-        <v>ac</v>
-      </c>
-      <c r="N4" s="1" t="str">
-        <f aca="false" t="array" ref="N4:N4">IF($I4="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I4,ROW($B$2:$B$13)-ROW($B$2)+1),4)),""))</f>
-        <v>ad</v>
-      </c>
-      <c r="O4" s="1" t="str">
-        <f aca="false" t="array" ref="O4:O4">IF($I4="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I4,ROW($B$2:$B$13)-ROW($B$2)+1),5)),""))</f>
-        <v>ae</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>2</v>
       </c>
@@ -516,36 +468,8 @@
       <c r="H5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="str">
-        <f aca="false">IFERROR(INDEX(_xlfn._xlws.SORT(_xlfn.UNIQUE($A$2:$A$13)),4),"")</f>
-        <v/>
-      </c>
-      <c r="J5" s="1" t="str">
-        <f aca="false">IF($I5="","",COUNTIF($A$2:$A$13,$I5))</f>
-        <v/>
-      </c>
-      <c r="K5" s="1" t="str">
-        <f aca="false" t="array" ref="K5:K5">IF($I5="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I5,ROW($B$2:$B$13)-ROW($B$2)+1),1)),""))</f>
-        <v/>
-      </c>
-      <c r="L5" s="1" t="str">
-        <f aca="false" t="array" ref="L5:L5">IF($I5="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I5,ROW($B$2:$B$13)-ROW($B$2)+1),2)),""))</f>
-        <v/>
-      </c>
-      <c r="M5" s="1" t="str">
-        <f aca="false" t="array" ref="M5:M5">IF($I5="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I5,ROW($B$2:$B$13)-ROW($B$2)+1),3)),""))</f>
-        <v/>
-      </c>
-      <c r="N5" s="1" t="str">
-        <f aca="false" t="array" ref="N5:N5">IF($I5="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I5,ROW($B$2:$B$13)-ROW($B$2)+1),4)),""))</f>
-        <v/>
-      </c>
-      <c r="O5" s="1" t="str">
-        <f aca="false" t="array" ref="O5:O5">IF($I5="","",IFERROR(INDEX($B$2:$B$13,SMALL(IF($A$2:$A$13=$I5,ROW($B$2:$B$13)-ROW($B$2)+1),5)),""))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>2</v>
       </c>
@@ -556,7 +480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>2</v>
       </c>
@@ -567,7 +491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>2</v>
       </c>
@@ -578,7 +502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>3</v>
       </c>
@@ -589,7 +513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>3</v>
       </c>
@@ -600,7 +524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>3</v>
       </c>
@@ -611,7 +535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>3</v>
       </c>
@@ -622,7 +546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>3</v>
       </c>
